--- a/Grelha_AutoAvaliacao_PRJ_MetaDigital.xlsx
+++ b/Grelha_AutoAvaliacao_PRJ_MetaDigital.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chewie\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E3ABEED-89C7-4047-BA34-E38676BFB119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7D234C7-7F00-4D12-B796-9EFF209871B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="54">
   <si>
     <t>#</t>
   </si>
@@ -185,13 +185,16 @@
   </si>
   <si>
     <t>Desenvolvimento do Portal do Aluno, Criação do do sistema de inquéritos de satisfação e avaliação dos alunos, Refresh automático de cada alteração na plataforma, Correção de criação de Sumários, Correção de gravação de Formadores/Coordenadores e Formandos, Correção de Avaliação Modular, Arquitetura e layout de diversos botões e popups da aplicação para melhor user experience, Ajuste de informações e detalhes de cada user, Correção de dados na DB, Testes intensivos e constantes de toda a aplicação e identificação de erros e problemas.</t>
+  </si>
+  <si>
+    <t>https://github.com/llm-Lucas/P4_UpskillPortal_26.git</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -260,6 +263,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="16"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -493,8 +511,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="55">
@@ -612,35 +631,36 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperligação" xfId="2" builtinId="8"/>
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -1294,7 +1314,7 @@
         <v>0.8</v>
       </c>
       <c r="H24" s="35">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="I24" s="29" t="s">
         <v>52</v>
@@ -1386,7 +1406,9 @@
     <row r="32" spans="4:9" x14ac:dyDescent="0.3">
       <c r="D32" s="44"/>
       <c r="E32" s="42"/>
-      <c r="F32" s="46"/>
+      <c r="F32" s="46" t="s">
+        <v>53</v>
+      </c>
       <c r="G32" s="47"/>
       <c r="H32" s="47"/>
       <c r="I32" s="48"/>
@@ -1570,9 +1592,12 @@
     <mergeCell ref="G18:I18"/>
     <mergeCell ref="G19:I19"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="F32" r:id="rId1" xr:uid="{B3C3EB32-AE94-4C0E-B79B-912A870AB7F1}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
